--- a/天平校验视频分析项目/参考/电子天平日常校验记录表.xlsx
+++ b/天平校验视频分析项目/参考/电子天平日常校验记录表.xlsx
@@ -684,7 +684,7 @@
     <t>/</t>
   </si>
   <si>
-    <t>40g</t>
+    <t>41g</t>
   </si>
   <si>
     <t>第二量程精度</t>
